--- a/out/MLP_Base_repeat_2_000006.xlsx
+++ b/out/MLP_Base_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.637571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004027647329891333</v>
+        <v>-0.0002990458658974385</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5183893747576593</v>
+        <v>0.3848953239618997</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.037760213456583</v>
+        <v>0.7705190550221372</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1197175113181193</v>
+        <v>-0.08888815074393581</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3982690987065509</v>
+        <v>0.2957081273520664</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3982690987065509</v>
+        <v>0.2957081273520664</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3978184702683326</v>
+        <v>0.2953892142534675</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.38442801931308</v>
+        <v>0.9797700100152706</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.169431228660438</v>
+        <v>2.256880185373564</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2648946401433958</v>
+        <v>0.1874679517072957</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.637571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.312772312243356</v>
+        <v>1.650616296187596</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4639883018494029</v>
+        <v>0.3283676789810402</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.975984000981671</v>
+        <v>2.119976033270114</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2540968789034325</v>
+        <v>0.1798263287674498</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.01978952705792</v>
+        <v>2.150977543276903</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1049457114729853</v>
+        <v>0.07427069583211837</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.975317698364222</v>
+        <v>2.119504486123321</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1307528602410806</v>
+        <v>0.09253540394521122</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.131896303697438</v>
+        <v>2.230316670628769</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07873070211397137</v>
+        <v>0.05571767559963609</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.158515137395398</v>
+        <v>2.249155005585543</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05985649864367362</v>
+        <v>0.04236130995918282</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.199463789976625</v>
+        <v>2.278134959370187</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02647389073034518</v>
+        <v>0.01873651763685776</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.19250387052905</v>
+        <v>2.273209322795969</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02100849236655257</v>
+        <v>0.01486596085094411</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.208035840720194</v>
+        <v>2.284200848658919</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01041616677692883</v>
+        <v>0.007369363816223279</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.207844848757382</v>
+        <v>2.284064213810678</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006054865153146334</v>
+        <v>0.004283161899057942</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.209532908070663</v>
+        <v>2.285257687036748</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003023477976200352</v>
+        <v>0.002139080949528971</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.209524137411145</v>
+        <v>2.285250017511228</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001492691692600867</v>
+        <v>0.001055745171918848</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.209481224850336</v>
+        <v>2.285218165812691</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008627897222547114</v>
+        <v>0.0006091281111341035</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.209716664476309</v>
+        <v>2.28538345858887</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.000285156114816348</v>
+        <v>0.0002003412504854155</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.209422369480391</v>
+        <v>2.285173403157752</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001409764245726178</v>
+        <v>9.830639277446798e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.209418998579312</v>
+        <v>2.285169560103375</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.57244722935807e-05</v>
+        <v>5.126251099249565e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.209427140025342</v>
+        <v>2.285173919938789</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.292288715141218e-05</v>
+        <v>2.344216536355913e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.037571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.209419580901163</v>
+        <v>2.285167057675914</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.209423726278256</v>
+        <v>2.285168511957807</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.637571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.209415724453838</v>
+        <v>2.285161509666987</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.637571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.209412619768588</v>
+        <v>2.285157647591891</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.209408300777438</v>
+        <v>2.285153100279706</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.209403476604549</v>
+        <v>2.285153190224356</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.209402618670965</v>
+        <v>2.285152332290771</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.209402846991999</v>
+        <v>2.285152560611805</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.037571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.209402051327787</v>
+        <v>2.285151764947594</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.20940211359716</v>
+        <v>2.285151827216966</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.209402141272437</v>
+        <v>2.285151854892244</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.20940229348646</v>
+        <v>2.285152007106266</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.209401947545499</v>
+        <v>2.285151661165305</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.20940202365251</v>
+        <v>2.285151737272316</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.209402189704171</v>
+        <v>2.285151903323978</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.209402549482772</v>
+        <v>2.285152263102578</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.637571854792519</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.209402570239229</v>
+        <v>2.285152283859036</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.209402674021518</v>
+        <v>2.285152387641324</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.209402902342552</v>
+        <v>2.285152615962359</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.209402777803807</v>
+        <v>2.285152491423613</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.209402805479083</v>
+        <v>2.28515251909889</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.134013026559911</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.209402860829637</v>
+        <v>2.285152574449444</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.209403123744768</v>
+        <v>2.285152837364575</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.209403040718937</v>
+        <v>2.285152754338744</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.209402833154361</v>
+        <v>2.285152546774166</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.209402846991999</v>
+        <v>2.285152560611805</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.209402985368383</v>
+        <v>2.28515269898819</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.209402701696795</v>
+        <v>2.285152415316601</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.209402528726314</v>
+        <v>2.285152242346121</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.209402424944026</v>
+        <v>2.285152138563832</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.209402570239229</v>
+        <v>2.285152283859036</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.209402812397903</v>
+        <v>2.285152526017709</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.209402639427422</v>
+        <v>2.285152353047228</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.209402341918195</v>
+        <v>2.285152055538001</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.209402328080556</v>
+        <v>2.285152041700363</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.209401961383137</v>
+        <v>2.285151675002943</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.209401961383137</v>
+        <v>2.285151675002943</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.209401899113764</v>
+        <v>2.28515161273357</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.209401795331476</v>
+        <v>2.285151508951281</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.209401622360995</v>
+        <v>2.285151335980801</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.20940167079273</v>
+        <v>2.285151384412536</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.209401311014129</v>
+        <v>2.285151024633936</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.209401269501214</v>
+        <v>2.28515098312102</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.209401324851768</v>
+        <v>2.285151038471574</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.209401380202321</v>
+        <v>2.285151093822128</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.209401421715237</v>
+        <v>2.285151135335044</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.209401151881287</v>
+        <v>2.285150865501093</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.209401207231841</v>
+        <v>2.285150920851647</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.209401352527045</v>
+        <v>2.285151066146851</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.209401317932949</v>
+        <v>2.285151031552755</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.20940130409531</v>
+        <v>2.285151017715116</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.209401394039959</v>
+        <v>2.285151107659766</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.637571854792519</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.209401712305644</v>
+        <v>2.285151425925451</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5384768609581863</v>
+        <v>1.734013026559911</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.209401532416345</v>
+        <v>2.285151246036151</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.20940157392926</v>
+        <v>2.285151287549066</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.066793665939915</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.209401387121141</v>
+        <v>2.285151100740948</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.209401456309334</v>
+        <v>2.285151169929139</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.209401255663576</v>
+        <v>2.285150969283382</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.209401297176491</v>
+        <v>2.285151010796297</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-1.666793665939915</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.209401324851768</v>
+        <v>2.285151038471574</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_2_000006.xlsx
+++ b/out/MLP_Base_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.637571854792519</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0004027647329891333</v>
+        <v>-0.0003023625293551013</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5183893747576593</v>
+        <v>0.3891639177253826</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.037760213456583</v>
+        <v>0.7790647426662703</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1197175113181193</v>
+        <v>-0.08987404170564862</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3982690987065509</v>
+        <v>0.2989875134903788</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3982690987065509</v>
+        <v>0.2989875134903788</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3978184702683326</v>
+        <v>0.2986646303068143</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.38442801931308</v>
+        <v>0.9919668073678721</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC49" t="n">
-        <v>3.169431228660438</v>
+        <v>2.28457380799088</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2648946401433958</v>
+        <v>0.1898016714514278</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.312772312243356</v>
+        <v>1.670762561456035</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4639883018494029</v>
+        <v>0.3324556279750738</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.037571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.975984000981671</v>
+        <v>2.145965496621355</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.2540968789034325</v>
+        <v>0.1820650383994816</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC52" t="n">
-        <v>3.01978952705792</v>
+        <v>2.177352953333142</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.1049457114729853</v>
+        <v>0.07519531551311923</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.975317698364222</v>
+        <v>2.145488079043985</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1307528602410806</v>
+        <v>0.09368691030213941</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC54" t="n">
-        <v>3.131896303697438</v>
+        <v>2.257679793431811</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.07873070211397137</v>
+        <v>0.0564122123542647</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC55" t="n">
-        <v>3.158515137395398</v>
+        <v>2.276752750472362</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05985649864367362</v>
+        <v>0.04288754856759631</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432805</v>
       </c>
       <c r="JC56" t="n">
-        <v>3.199463789976625</v>
+        <v>2.306093327089447</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02647389073034518</v>
+        <v>0.01897006873434084</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC57" t="n">
-        <v>3.19250387052905</v>
+        <v>2.301106292348825</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.02100849236655257</v>
+        <v>0.01505260452512489</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC58" t="n">
-        <v>3.208035840720194</v>
+        <v>2.312234888546155</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.01041616677692883</v>
+        <v>0.007461918585965566</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC59" t="n">
-        <v>3.207844848757382</v>
+        <v>2.312096622581442</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.006054865153146334</v>
+        <v>0.004335527512479275</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC60" t="n">
-        <v>3.209532908070663</v>
+        <v>2.313304726180838</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.003023477976200352</v>
+        <v>0.002165263756239637</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC61" t="n">
-        <v>3.209524137411145</v>
+        <v>2.313297024055957</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001492691692600867</v>
+        <v>0.001067243764568375</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC62" t="n">
-        <v>3.209481224850336</v>
+        <v>2.313264846688</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0008627897222547114</v>
+        <v>0.0006191410694678117</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC63" t="n">
-        <v>3.209716664476309</v>
+        <v>2.313432444857888</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.000285156114816348</v>
+        <v>0.0002025732205993874</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.637571854792519</v>
+        <v>1.762906414714871</v>
       </c>
       <c r="JC64" t="n">
-        <v>3.209422369480391</v>
+        <v>2.313220172596117</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001409764245726178</v>
+        <v>0.000100552183921739</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC65" t="n">
-        <v>3.209418998579312</v>
+        <v>2.313216340554276</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>7.57244722935807e-05</v>
+        <v>5.126251099249565e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.138476860958186</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC66" t="n">
-        <v>3.209427140025342</v>
+        <v>2.31322070038969</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>3.292288715141218e-05</v>
+        <v>2.344216536355913e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.037571854792519</v>
+        <v>0.8369524225432804</v>
       </c>
       <c r="JC67" t="n">
-        <v>3.209419580901163</v>
+        <v>2.313213838126814</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.827360596503633e-05</v>
+        <v>1.245520447377725e-05</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>2.037571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC68" t="n">
-        <v>3.209423726278256</v>
+        <v>2.313215292408708</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>2.732487839350877e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.637571854792519</v>
+        <v>1.56290641471487</v>
       </c>
       <c r="JC69" t="n">
-        <v>3.209415724453838</v>
+        <v>2.313208290117887</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC70" t="n">
-        <v>3.209412619768588</v>
+        <v>2.313204428042791</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC71" t="n">
-        <v>3.209408300777438</v>
+        <v>2.313199880730606</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>-1.724541871943372e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC72" t="n">
-        <v>3.209403476604549</v>
+        <v>2.313199970675256</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC73" t="n">
-        <v>3.209402618670965</v>
+        <v>2.313199112741671</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC74" t="n">
-        <v>3.209402846991999</v>
+        <v>2.313199341062706</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>2.037571854792519</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC75" t="n">
-        <v>3.209402051327787</v>
+        <v>2.313198545398494</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC76" t="n">
-        <v>3.20940211359716</v>
+        <v>2.313198607667867</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC77" t="n">
-        <v>3.209402141272437</v>
+        <v>2.313198635343144</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC78" t="n">
-        <v>3.20940229348646</v>
+        <v>2.313198787557167</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC79" t="n">
-        <v>3.209401947545499</v>
+        <v>2.313198441616206</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC80" t="n">
-        <v>3.20940202365251</v>
+        <v>2.313198517723217</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC81" t="n">
-        <v>3.209402189704171</v>
+        <v>2.313198683774879</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.1109984303716907</v>
       </c>
       <c r="JC82" t="n">
-        <v>3.209402549482772</v>
+        <v>2.313199043553479</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.637571854792519</v>
+        <v>1.03695242254328</v>
       </c>
       <c r="JC83" t="n">
-        <v>3.209402570239229</v>
+        <v>2.313199064309936</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.637571854792519</v>
+        <v>1.036952422543281</v>
       </c>
       <c r="JC84" t="n">
-        <v>3.209402674021518</v>
+        <v>2.313199168092225</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC85" t="n">
-        <v>3.209402902342552</v>
+        <v>2.31319939641326</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC86" t="n">
-        <v>3.209402777803807</v>
+        <v>2.313199271874514</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC87" t="n">
-        <v>3.209402805479083</v>
+        <v>2.313199299549791</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC88" t="n">
-        <v>3.209402860829637</v>
+        <v>2.313199354900344</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC89" t="n">
-        <v>3.209403123744768</v>
+        <v>2.313199617815475</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC90" t="n">
-        <v>3.209403040718937</v>
+        <v>2.313199534789644</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC91" t="n">
-        <v>3.209402833154361</v>
+        <v>2.313199327225067</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC92" t="n">
-        <v>3.209402846991999</v>
+        <v>2.313199341062706</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC93" t="n">
-        <v>3.209402985368383</v>
+        <v>2.313199479439091</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC94" t="n">
-        <v>3.209402701696795</v>
+        <v>2.313199195767502</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC95" t="n">
-        <v>3.209402528726314</v>
+        <v>2.313199022797021</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC96" t="n">
-        <v>3.209402424944026</v>
+        <v>2.313198919014733</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC97" t="n">
-        <v>3.209402570239229</v>
+        <v>2.313199064309936</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC98" t="n">
-        <v>3.209402812397903</v>
+        <v>2.31319930646861</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC99" t="n">
-        <v>3.209402639427422</v>
+        <v>2.313199133498129</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC100" t="n">
-        <v>3.209402341918195</v>
+        <v>2.313198835988902</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC101" t="n">
-        <v>3.209402328080556</v>
+        <v>2.313198822151263</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC102" t="n">
-        <v>3.209401961383137</v>
+        <v>2.313198455453844</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC103" t="n">
-        <v>3.209401961383137</v>
+        <v>2.313198455453844</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC104" t="n">
-        <v>3.209401899113764</v>
+        <v>2.313198393184471</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC105" t="n">
-        <v>3.209401795331476</v>
+        <v>2.313198289402182</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC106" t="n">
-        <v>3.209401622360995</v>
+        <v>2.313198116431701</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC107" t="n">
-        <v>3.20940167079273</v>
+        <v>2.313198164863436</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC108" t="n">
-        <v>3.209401311014129</v>
+        <v>2.313197805084836</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC109" t="n">
-        <v>3.209401269501214</v>
+        <v>2.313197763571921</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC110" t="n">
-        <v>3.209401324851768</v>
+        <v>2.313197818922474</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC111" t="n">
-        <v>3.209401380202321</v>
+        <v>2.313197874273029</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC112" t="n">
-        <v>3.209401421715237</v>
+        <v>2.313197915785944</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC113" t="n">
-        <v>3.209401151881287</v>
+        <v>2.313197645951994</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC114" t="n">
-        <v>3.209401207231841</v>
+        <v>2.313197701302547</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC115" t="n">
-        <v>3.209401352527045</v>
+        <v>2.313197846597752</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC116" t="n">
-        <v>3.209401317932949</v>
+        <v>2.313197812003655</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC117" t="n">
-        <v>3.20940130409531</v>
+        <v>2.313197798166017</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.138476860958186</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC118" t="n">
-        <v>3.209401394039959</v>
+        <v>2.313197888110667</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.637571854792519</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC119" t="n">
-        <v>3.209401712305644</v>
+        <v>2.313198206376351</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5384768609581863</v>
+        <v>0.3109984303716907</v>
       </c>
       <c r="JC120" t="n">
-        <v>3.209401532416345</v>
+        <v>2.313198026487052</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5384768609581863</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC121" t="n">
-        <v>3.20940157392926</v>
+        <v>2.313198067999967</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.414955561799899</v>
       </c>
       <c r="JC122" t="n">
-        <v>3.209401387121141</v>
+        <v>2.313197881191848</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC123" t="n">
-        <v>3.209401456309334</v>
+        <v>2.31319795038004</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC124" t="n">
-        <v>3.209401255663576</v>
+        <v>2.313197749734282</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC125" t="n">
-        <v>3.209401297176491</v>
+        <v>2.313197791247198</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.138476860958186</v>
+        <v>-0.6149555617998991</v>
       </c>
       <c r="JC126" t="n">
-        <v>3.209401324851768</v>
+        <v>2.313197818922474</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_2_000006.xlsx
+++ b/out/MLP_Base_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4124981760978699</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-1</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4146312177181244</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4336269199848175</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4618782103061676</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.415528416633606</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4415021538734436</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3875909745693207</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4511305391788483</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4569327831268311</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4149897992610931</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.3888840973377228</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3674860596656799</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4202429056167603</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3783861994743347</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.3700526356697083</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3659718632698059</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.3967108130455017</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4224564433097839</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4670504331588745</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4178466796875</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4005920886993408</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3739299476146698</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3802894055843353</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4480275511741638</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3894069194793701</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4771960377693176</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5717604160308838</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.03695242254328</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.50893235206604</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.036952422543281</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4541364014148712</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4590891003608704</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.414955561799899</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4042438566684723</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3803687989711761</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4051182270050049</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5229856371879578</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4620379209518433</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4535146057605743</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4861786365509033</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4307518899440765</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4490244388580322</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4905887842178345</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.1109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5427269339561462</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.03695242254328</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5607047080993652</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.612349808216095</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003023625293551013</v>
+        <v>-0.0002147892381881829</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3891639177253826</v>
+        <v>0.2764504808246421</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5915477275848389</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.762906414714871</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.7790647426662703</v>
+        <v>0.5534241389394077</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08987404170564862</v>
+        <v>-0.06384377903018326</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5185865759849548</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2989875134903788</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5615096092224121</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.762906414714871</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2989875134903788</v>
+        <v>0.2123919125562706</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.5559513568878174</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2986646303068143</v>
+        <v>0.2122727167830646</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.9919668073678721</v>
+        <v>0.3661950314083699</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5061808228492737</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.28457380799088</v>
+        <v>0.9453922846818488</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1898016714514278</v>
+        <v>0.07006735519795214</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.5768459439277649</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.16</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.670762561456035</v>
+        <v>0.718797248674785</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3324556279750738</v>
+        <v>0.1227294001466499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5517497062683105</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.145965496621355</v>
+        <v>0.8942234757282896</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1820650383994816</v>
+        <v>0.06721132397827324</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5608978867530823</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.177352953333142</v>
+        <v>0.9058105027624485</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.07519531551311923</v>
+        <v>0.02775905880951137</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5315638184547424</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.145488079043985</v>
+        <v>0.8940472319822265</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.09368691030213941</v>
+        <v>0.03458540515472364</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6204937696456909</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.257679793431811</v>
+        <v>0.935464230815531</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0564122123542647</v>
+        <v>0.02082547197424655</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5175610780715942</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.276752750472362</v>
+        <v>0.9425053184761174</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04288754856759631</v>
+        <v>0.01583205915755942</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6515496373176575</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8369524225432805</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.306093327089447</v>
+        <v>0.9533368633026545</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01897006873434084</v>
+        <v>0.007000599424997798</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4324300289154053</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.301106292348825</v>
+        <v>0.951492997726175</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01505260452512489</v>
+        <v>0.005553954836411267</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3229359984397888</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.312234888546155</v>
+        <v>0.9555982901916548</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.007461918585965566</v>
+        <v>0.002751631250162162</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.7258776426315308</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8369524225432804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.312096622581442</v>
+        <v>0.9555440911654862</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004335527512479275</v>
+        <v>0.001597969610841877</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7117645144462585</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.313304726180838</v>
+        <v>0.9559869431489801</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002165263756239637</v>
+        <v>0.0007950302050481237</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5716777443885803</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.762906414714871</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.313297024055957</v>
+        <v>0.9559809470573687</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001067243764568375</v>
+        <v>0.0003917014464086749</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5690056085586548</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.762906414714871</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.313264846688</v>
+        <v>0.9559659049587285</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006191410694678117</v>
+        <v>0.0002252980416752888</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5827127695083618</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.762906414714871</v>
+        <v>0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.313432444857888</v>
+        <v>0.9560245909144622</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002025732205993874</v>
+        <v>7.088698387504487e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.5016388893127441</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.762906414714871</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.313220172596117</v>
+        <v>0.9559431116611959</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.000100552183921739</v>
+        <v>3.317844950360773e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.509837806224823</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.313216340554276</v>
+        <v>0.9559385479517856</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.126251099249565e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4653940200805664</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.03695242254328</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.31322070038969</v>
+        <v>0.9559371319825209</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.344216536355913e-05</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5114328265190125</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.8369524225432804</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.313213838126814</v>
+        <v>0.9559314351212175</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.523667573928833</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.313215292408708</v>
+        <v>0.9559291262164156</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.5062317252159119</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.56290641471487</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.313208290117887</v>
+        <v>0.9559231266828189</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.533316969871521</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.313204428042791</v>
+        <v>0.9559188840726649</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.440563440322876</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.313199880730606</v>
+        <v>0.9559191123936995</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4618494808673859</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.313199970675256</v>
+        <v>0.9559192023383496</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4579814076423645</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.313199112741671</v>
+        <v>0.9559183444047648</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.489408403635025</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.313199341062706</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5136365294456482</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.313198545398494</v>
+        <v>0.9559177770615876</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4345190823078156</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.313198607667867</v>
+        <v>0.9559178393309608</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4502228498458862</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.313198635343144</v>
+        <v>0.9559178670062376</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.4895590543746948</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.313198787557167</v>
+        <v>0.9559180192202609</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4322187900543213</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.313198441616206</v>
+        <v>0.9559176732792992</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4501693248748779</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.313198517723217</v>
+        <v>0.9559177493863108</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3938216865062714</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.313198683774879</v>
+        <v>0.9559179154379724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4860360026359558</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1109984303716907</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.313199043553479</v>
+        <v>0.9559182752165725</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5021764039993286</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.03695242254328</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.313199064309936</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5274709463119507</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.036952422543281</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.313199168092225</v>
+        <v>0.9559183997553187</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4336036145687103</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3109984303716907</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.31319939641326</v>
+        <v>0.9559186280763533</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.404813826084137</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.414955561799899</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.313199271874514</v>
+        <v>0.9559185035376071</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3677560091018677</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.313199299549791</v>
+        <v>0.9559185312128839</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>0.4740111827850342</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.313199354900344</v>
+        <v>0.955918586563438</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.4024321436882019</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.313199617815475</v>
+        <v>0.9559188494785686</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4131218492984772</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.313199534789644</v>
+        <v>0.9559187664527379</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3907667696475983</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.313199327225067</v>
+        <v>0.9559185588881611</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.3804031014442444</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.313199341062706</v>
+        <v>0.9559185727257994</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3718409240245819</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.313199479439091</v>
+        <v>0.9559187111021842</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3715291619300842</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.313199195767502</v>
+        <v>0.9559184274305955</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3578914403915405</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.313199022797021</v>
+        <v>0.9559182544601148</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4312702417373657</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.313198919014733</v>
+        <v>0.9559181506778263</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3901233077049255</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.313199064309936</v>
+        <v>0.9559182959730301</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.357559472322464</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.31319930646861</v>
+        <v>0.9559185381317034</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3699121475219727</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.313199133498129</v>
+        <v>0.9559183651612224</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3560536205768585</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.313198835988902</v>
+        <v>0.9559180676519955</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3837195336818695</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.313198822151263</v>
+        <v>0.9559180538143569</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3730451166629791</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.313198455453844</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4024307131767273</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.313198455453844</v>
+        <v>0.9559176871169377</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4551804959774017</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.313198393184471</v>
+        <v>0.9559176248475646</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3822465837001801</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.313198289402182</v>
+        <v>0.9559175210652762</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.3936318457126617</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.313198116431701</v>
+        <v>0.9559173480947953</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4064489006996155</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.313198164863436</v>
+        <v>0.95591739652653</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3991659283638</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.313197805084836</v>
+        <v>0.9559170367479298</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3876476287841797</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.313197763571921</v>
+        <v>0.9559169952350145</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4234979152679443</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.313197818922474</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3693552911281586</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.313197874273029</v>
+        <v>0.9559171059361221</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3764719367027283</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.313197915785944</v>
+        <v>0.9559171474490376</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3803161680698395</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.313197645951994</v>
+        <v>0.9559168776150875</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3877521455287933</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.313197701302547</v>
+        <v>0.9559169329656414</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3726904690265656</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.313197846597752</v>
+        <v>0.9559170782608453</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3784593045711517</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.313197812003655</v>
+        <v>0.955917043666749</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3678034245967865</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.313197798166017</v>
+        <v>0.9559170298291105</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.4520526528358459</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.313197888110667</v>
+        <v>0.9559171197737607</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5391400456428528</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.313198206376351</v>
+        <v>0.9559174380394453</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4448697566986084</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3109984303716907</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.313198026487052</v>
+        <v>0.9559172581501452</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4323015809059143</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.414955561799899</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.313198067999967</v>
+        <v>0.9559172996630606</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4329961836338043</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.414955561799899</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.313197881191848</v>
+        <v>0.9559171128549413</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3895063996315002</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6149555617998991</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.31319795038004</v>
+        <v>0.9559171820431338</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4206153452396393</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.313197749734282</v>
+        <v>0.9559169813973759</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3903748691082001</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.313197791247198</v>
+        <v>0.9559170229102913</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4159793555736542</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6149555617998991</v>
+        <v>-0.7200000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.313197818922474</v>
+        <v>0.9559170505855682</v>
       </c>
     </row>
   </sheetData>
